--- a/excels/1급_기출문제_분개.xlsx
+++ b/excels/1급_기출문제_분개.xlsx
@@ -4559,14 +4559,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>보통예금
-[제</t>
+          <t>보통예금</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1800000
-118</t>
+          <t>1800000</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -4602,15 +4600,13 @@
       <c r="D8" t="inlineStr">
         <is>
           <t>미지급금(신한카드)
-현금
-[제</t>
+현금</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>17800000
-2000000
-118</t>
+2000000</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -4741,14 +4737,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>미지급금(비씨카드)
-[제</t>
+          <t>미지급금(비씨카드)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>550000
-118</t>
+          <t>550000</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -4797,16 +4791,14 @@
         <is>
           <t>현금
 (출금) 차량유지비
-부가세대급급
-[제</t>
+부가세대급급</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>275000
 250000
-25000
-118</t>
+25000</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -4853,14 +4845,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>제품매출
-[제</t>
+          <t>제품매출</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>50000000
-118</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -4895,9 +4885,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>보통예금
-[제
-문제</t>
+          <t>보통예금</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -4947,14 +4935,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>미수금(
-[제</t>
+          <t>미수금(</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>120
-119</t>
+          <t>120</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -4983,8 +4969,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>630000
-951</t>
+          <t>630000</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -5066,15 +5051,13 @@
       <c r="D17" t="inlineStr">
         <is>
           <t>당좌예금
-당좌차월
-[제</t>
+당좌차월</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>4000000
-1000000
-119</t>
+1000000</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -5169,14 +5152,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>대손충당금(
-[제</t>
+          <t>대손충당금(</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>121
-119</t>
+          <t>121</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -5257,14 +5238,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>보통예금
-[제</t>
+          <t>보통예금</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>800000
-119</t>
+          <t>800000</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -5347,14 +5326,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>미지급금(국민카드)
-[제</t>
+          <t>미지급금(국민카드)</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>850000
-119</t>
+          <t>850000</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -5571,15 +5548,13 @@
       <c r="D28" t="inlineStr">
         <is>
           <t>가지급금
-현금
-[제</t>
+현금</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>500000
-150000
-120</t>
+150000</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -5697,15 +5672,13 @@
       <c r="D31" t="inlineStr">
         <is>
           <t>정기예금
-이자수익
-[제</t>
+이자수익</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>30000000
-1200000
-120</t>
+1200000</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -5843,8 +5816,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>11000000
-207</t>
+          <t>11000000</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5902,14 +5874,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>보통예금
-[제</t>
+          <t>보통예금</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>23100000
-120</t>
+          <t>23100000</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -5950,14 +5920,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>보통예금
-[제</t>
+          <t>보통예금</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>5500000
-120</t>
+          <t>5500000</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -5998,9 +5966,7 @@
       <c r="D37" t="inlineStr">
         <is>
           <t>부가세예수금
-제품매출
-[제
-문제</t>
+제품매출</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -6086,15 +6052,13 @@
       <c r="D39" t="inlineStr">
         <is>
           <t>외상매출금(HONEY사)
-외환차익
-[제</t>
+외환차익</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
           <t>13000000
-500000
-121</t>
+500000</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -6246,20 +6210,17 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>109
-835</t>
+          <t>109</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>외상매출금(㈜금호전자)
-[제</t>
+          <t>외상매출금(㈜금호전자)</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>15000000
-121</t>
+          <t>15000000</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -6296,14 +6257,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>제품매출
-[제</t>
+          <t>제품매출</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>50000000
-121</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -6348,16 +6307,14 @@
         <is>
           <t>현금
 운반비
-부가세대급금
-[제</t>
+부가세대급금</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
           <t>110000
 100000
-10000
-121</t>
+10000</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -6406,14 +6363,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>보통예금
-[제</t>
+          <t>보통예금</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1100000
-121</t>
+          <t>1100000</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -6505,15 +6460,13 @@
       <c r="D48" t="inlineStr">
         <is>
           <t>제품매출
-부가세예수금
-[제</t>
+부가세예수금</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
           <t>3000000
-300000
-121</t>
+300000</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -6646,14 +6599,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>보통예금
-[제</t>
+          <t>보통예금</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>7000000
-122</t>
+          <t>7000000</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -6697,8 +6648,7 @@
 예수금
 예수금
 보통예금
-보통예금
-[제</t>
+보통예금</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -6708,8 +6658,7 @@
 442810
 360900
 3157190
-2639100
-122</t>
+2639100</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -6776,8 +6725,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1500000
-109</t>
+          <t>1500000</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -6855,14 +6803,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>받을어음(㈜아름전자)
-[제</t>
+          <t>받을어음(㈜아름전자)</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>5000000
-122</t>
+          <t>5000000</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -6945,14 +6891,12 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>미지급금
-[제</t>
+          <t>미지급금</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>3300000
-122</t>
+          <t>3300000</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -6998,14 +6942,12 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>보통예금
-[제</t>
+          <t>보통예금</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>288200
-122</t>
+          <t>288200</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -7092,14 +7034,12 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>제품매출
-[제</t>
+          <t>제품매출</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>65000000
-122</t>
+          <t>65000000</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -7143,9 +7083,7 @@
       <c r="D61" t="inlineStr">
         <is>
           <t>제품매출
-부가세예수금
-[제
-문제</t>
+부가세예수금</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -7276,14 +7214,12 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>보통예금
-[제</t>
+          <t>보통예금</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>6500000
-123</t>
+          <t>6500000</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -7398,14 +7334,12 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>보통예금
-[제</t>
+          <t>보통예금</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>30000000
-123</t>
+          <t>30000000</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -7479,14 +7413,12 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>미지급금(국민카드)
-[제</t>
+          <t>미지급금(국민카드)</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>550000
-123</t>
+          <t>550000</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -7528,15 +7460,13 @@
       <c r="D70" t="inlineStr">
         <is>
           <t>제품매출
-부가세예수금
-[제</t>
+부가세예수금</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
           <t>800000
-80000
-123</t>
+80000</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -7612,14 +7542,12 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>미지급금(하나카드)
-[제</t>
+          <t>미지급금(하나카드)</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>1100000
-123</t>
+          <t>1100000</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -7679,47 +7607,7 @@
 제품매출
 문제
 [
-송비와 관련한 전자세금계산서는 정상적으로 발급받았다. (
-[제
-현금
-공급가액:
-부가세:
-현금
-[
-것). (
-보통예금
-보통예금
-문제
-결산정리사항은 다음과 같다. 관련 메뉴를 이용하여 결산을 완료하시오. (
-[
-보험료
-ㆍ
-[
-단기매매증권
-[제
-[
-각범위액’을 감가상각비로 반영하시오. (
-ㆍ취득년월일：
-ㆍ코드번호：
-ㆍ취득원가：
-ㆍ전기말감가상각누계액：
-ㆍ내용연수：
-ㆍ감가상각방법：정액법
-또는
-감가상각누계액(기계장치)
-ㆍ감가상각비：
-문제
-메뉴에 입력하시오. (
-[
-마인가? (
-ㆍ
-[제
-[
-큰 수에서 작은 수를 뺄 것. (
-ㆍ[총계정원장] 조회 &gt; 기간：
-&gt;
-ㆍ
-[</t>
+송비와 관련한 전자세금계산서는 정상적으로 발급받았다. (</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -7953,15 +7841,13 @@
       <c r="D75" t="inlineStr">
         <is>
           <t>외상매출금(ST그룹)
-외환차익
-[제</t>
+외환차익</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
           <t>22000000
-1000000
-124</t>
+1000000</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -8101,20 +7987,17 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>12100000
-984</t>
+          <t>12100000</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>당좌예금
-[제</t>
+          <t>당좌예금</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>12130000
-124</t>
+          <t>12130000</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -8151,15 +8034,13 @@
       <c r="D80" t="inlineStr">
         <is>
           <t>제품매출
-부가세예수금
-[제</t>
+부가세예수금</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
           <t>4000000
-400000
-124</t>
+400000</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -8226,14 +8107,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>운반비
-[제</t>
+          <t>운반비</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>30000
-124</t>
+          <t>30000</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -8324,14 +8203,12 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>제품매출
-[제</t>
+          <t>제품매출</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>15000000
-124</t>
+          <t>15000000</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -8508,14 +8385,12 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>자본금
-[제</t>
+          <t>자본금</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>100000000
-125</t>
+          <t>100000000</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -8637,8 +8512,7 @@
           <t>보통예금
 예수금
 보통예금
-예수금
-[제</t>
+예수금</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -8646,8 +8520,7 @@
           <t>6760000
 240000
 6760000
-240000
-125</t>
+240000</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -8705,15 +8578,13 @@
       <c r="D92" t="inlineStr">
         <is>
           <t>제품매출
-부가세예수금
-[제</t>
+부가세예수금</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
           <t>20000000
-2000000
-125</t>
+2000000</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -8801,14 +8672,12 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>미지급금(우리카드(법인))
-[제</t>
+          <t>미지급금(우리카드(법인))</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>440000
-125</t>
+          <t>440000</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -8894,14 +8763,12 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>보통예금
-[제</t>
+          <t>보통예금</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>1000000
-125</t>
+          <t>1000000</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -8956,52 +8823,7 @@
       <c r="D97" t="inlineStr">
         <is>
           <t>제품매출
-부가세예수금
-[제
-문제
-[
-확인되었다. (
-공급가액:
-외상매입금
-ㆍ수정 후：매입매출전표입력
-부가세:
-선급금
-[
-산부의 화물차 주유분으로 확인되었다. (
-현금
-현금
-또는&lt;출금전표&gt; 차량유지비
-부가세대급금
-[제
-문제
-결산정리사항은 다음과 같다. 관련 메뉴를 이용하여 결산을 완료하시오. (
-[
-말 보유 중이다(결산일 현재 적용환율은
-외상매출금(NEW WORLD)
-외화환산이익
-ㆍ$
-[
-이자수익
-ㆍ이자수익 :
-[
-있으며
-&gt;선납세금
-또는
-선납세금
-미지급세금
-[제
-문제
-메뉴에 입력하시오. (
-[
-(
-ㆍ[총계정원장] &gt; 기간：
-ㆍ
-[
-ㆍ[계정별원장] &gt; 기간 :
-ㆍ[총계정원장] ＞ 기간 :
-[
-는 얼마인가? (
-ㆍ[세금계산서합계표] &gt; [매출] &gt; 기간 :</t>
+부가세예수금</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -9301,15 +9123,13 @@
       <c r="D100" t="inlineStr">
         <is>
           <t>보통예금
-ㆍ보통예금 이체금액 :
-[제</t>
+ㆍ보통예금 이체금액 :</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
           <t>3600000
-3500000
-126</t>
+3500000</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -9428,15 +9248,13 @@
       <c r="D103" t="inlineStr">
         <is>
           <t>현금
-(출금전표) 선급금(㈜우도)
-[제</t>
+(출금전표) 선급금(㈜우도)</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
           <t>500000
-500000
-126</t>
+500000</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -9476,15 +9294,13 @@
       <c r="D104" t="inlineStr">
         <is>
           <t>현금
-미지급금
-[제</t>
+미지급금</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
           <t>220000
-700000
-126</t>
+700000</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -9574,8 +9390,7 @@
           <t>제품매출
 부가세예수금
 (입금전표) 제품매출
-부가세예수금
-[제</t>
+부가세예수금</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -9583,8 +9398,7 @@
           <t>30000
 3000
 30000
-3000
-126</t>
+3000</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -9635,15 +9449,13 @@
       <c r="D107" t="inlineStr">
         <is>
           <t>보통예금
-당좌예금
-[제</t>
+당좌예금</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
           <t>12000000
-10000000
-126</t>
+10000000</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -9689,14 +9501,12 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>미지급금(우리카드(법인))
-[제</t>
+          <t>미지급금(우리카드(법인))</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>440000
-126</t>
+          <t>440000</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -9758,44 +9568,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>보통예금
-[제
-문제
-[
-었다. (
-유형 :
-제품매출
-유형 :
-제품매출
-[
-유형 :
-현금
-유형 :
-미지급금
-[제
-문제
-결산정리사항은 다음과 같다. 관련 메뉴를 이용하여 결산을 완료하시오. (
-[
-보험료
-ㆍ선급비용 :
-[
-중
-그 원인이 파악되지 않아 당기의 비용으로 대체한다. (
-현금과부족
-[
-감가상각누계액(
-또는
-&gt;
-[제
-문제
-메뉴에 입력하시오. (
-[
-ㆍ[매입매출장] &gt; 조회기간 :
-[
-ㆍ[재무상태표] &gt; 기간
-[
-ㆍ[제조원가명세서] &gt; 기간 :
-ㆍ[합계잔액시산표] &gt; 기간 :</t>
+          <t>보통예금</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -10111,14 +9884,12 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>받을어음(㈜제이디)
-[제</t>
+          <t>받을어음(㈜제이디)</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2200000
-127</t>
+          <t>2200000</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -10148,8 +9919,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>4500000
-984</t>
+          <t>4500000</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -10196,14 +9966,12 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>보통예금
-[제</t>
+          <t>보통예금</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>5000000
-127</t>
+          <t>5000000</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -10240,14 +10008,12 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>보통예금
-[제</t>
+          <t>보통예금</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>330000
-127</t>
+          <t>330000</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -10328,14 +10094,12 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>제품매출
-[제</t>
+          <t>제품매출</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>20000000
-127</t>
+          <t>20000000</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -10379,15 +10143,13 @@
       <c r="D119" t="inlineStr">
         <is>
           <t>부가세예수금
-제품매출
-[제</t>
+제품매출</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
           <t>450000
-4500000
-127</t>
+4500000</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -10432,15 +10194,13 @@
       <c r="D120" t="inlineStr">
         <is>
           <t>제품매출
-부가세예수금
-[제</t>
+부가세예수금</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
           <t>2000000
-200000
-127</t>
+200000</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -10470,116 +10230,24 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>외주가공비
-부가세대급금
-외상매입금(기장간판)
-미지급금(기장간판)
-복리후생비
-복리후생비
-부가세대급금
-장기차입금(UNK사)
-선급비용
-장기차입금
-ㆍ[일계표(월계표)] &gt; [일계표] 탭 &gt; 조회기간 :
-ㆍ[일계표(월계표)] &gt; [월계표] 탭 &gt; 조회기간 :
-[
-ㆍ[거래처원장] ＞ 잔액 탭 ＞ 기간：</t>
+          <t>외주가공비(제)
+부가세대급금</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
           <t>15000000
-1500000
-4100000
-4100000
-1100000
-1000000
-100000
-4000000
-1200000
-50000000
-2026
-2026
-3
-2026</t>
+1500000</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>미지급금(우리카드)
-[제
-문제
-[
-간판(거래처：기장간판)에 대한 대금 지급액으로 확인되었다. (
-보통예금
-보통예금
-[
-과세매입(전자세금계산서 발급)으로 확인되었다. (
-유형 :
-현금
-유형 :
-현금
-(출금전표) 복리후생비
-부가세대급금
-[제
-문제
-결산정리사항은 다음과 같다. 관련 메뉴를 이용하여 결산을 완료하시오. (
-[
-외화환산이익
-[
-임차료
-ㆍ선급비용 =
-[
-“코코은행 차입금 중 결산일로부터
-“코코은행 장기차입금
-유동성장기부채
-[제
-문제
-메뉴에 입력하시오. (
-[
-얼마인가? (
-ㆍ[부가가치세신고서] ＞ 조회기간 ：
-＞
-[</t>
+          <t>미지급금(우리카드)</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>16500000
-127
-4
-1
-3
-4100000
-4100000
-2
-3
-53
-1100000
-51
-1100000
-1000000
-100000
-127
-5
-9
-1
-4000000
-2
-1200000
-3600000
-3
-1
-1
-50000000
-127
-6
-9
-1
-3
-2026
-7
-2</t>
+          <t>16500000</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
